--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mithu\OneDrive\Desktop\College\DSA0603 - DATA HANDLING AND VISUALIZATION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd0aea9540a49ece/Desktop/College/DSA0603 - DATA HANDLING AND VISUALIZATION/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FDCA85-2535-4329-86A1-F02DCF8DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{84FDCA85-2535-4329-86A1-F02DCF8DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17EB5BEB-DCF8-4468-80B1-69B2027E045B}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="600" windowWidth="11415" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,49 +25,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>STUDENT</t>
-  </si>
-  <si>
-    <t>GRADE</t>
-  </si>
-  <si>
-    <t>RAM</t>
-  </si>
-  <si>
-    <t>JOHN</t>
-  </si>
-  <si>
-    <t>RAVI</t>
-  </si>
-  <si>
-    <t>SHAM</t>
-  </si>
-  <si>
-    <t>JEAN</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Pass_Percentage</t>
+  </si>
+  <si>
+    <t>CSE</t>
+  </si>
+  <si>
+    <t>ECE</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>MECH</t>
+  </si>
+  <si>
+    <t>CIVIL</t>
+  </si>
+  <si>
+    <t>AIDS</t>
+  </si>
+  <si>
+    <t>IT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +105,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -113,6 +140,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -378,74 +409,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2">
+        <v>91</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>93</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>92</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>89</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" s="2">
+        <v>95</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="C8" s="2">
+        <v>94</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd0aea9540a49ece/Desktop/College/DSA0603 - DATA HANDLING AND VISUALIZATION/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{84FDCA85-2535-4329-86A1-F02DCF8DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17EB5BEB-DCF8-4468-80B1-69B2027E045B}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{84FDCA85-2535-4329-86A1-F02DCF8DDCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1846F294-6B22-491B-9E84-7217835E2EF5}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="600" windowWidth="11415" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,36 +25,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>S.No</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Pass_Percentage</t>
-  </si>
-  <si>
-    <t>CSE</t>
-  </si>
-  <si>
-    <t>ECE</t>
-  </si>
-  <si>
-    <t>EEE</t>
-  </si>
-  <si>
-    <t>MECH</t>
-  </si>
-  <si>
-    <t>CIVIL</t>
-  </si>
-  <si>
-    <t>AIDS</t>
-  </si>
-  <si>
-    <t>IT</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Categorical</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Continent</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Temporal</t>
+  </si>
+  <si>
+    <t>Life Expectancy</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Adult Mortality</t>
+  </si>
+  <si>
+    <t>Infant Deaths</t>
+  </si>
+  <si>
+    <t>Alcohol</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>GDP</t>
+  </si>
+  <si>
+    <t>Schooling</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Developing</t>
   </si>
 </sst>
 </file>
@@ -109,7 +142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -122,6 +155,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -413,135 +449,165 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2">
-        <v>91</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2">
-        <v>93</v>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>92</v>
+        <v>9</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2015</v>
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>68.3</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5">
+        <v>181</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5">
+        <v>24.5</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1613</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10.1</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1311000000</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>89</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2">
-        <v>90</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2">
-        <v>94</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
